--- a/data/06_infrastructure.xlsx
+++ b/data/06_infrastructure.xlsx
@@ -2,23 +2,23 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="Red31e2cab42e42ed"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assets" sheetId="2" r:id="R269e8715d9f44962"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Asset Constraints" sheetId="3" r:id="R1dc2d1cf0ed54dab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Infrastructure Connections" sheetId="4" r:id="Rf90b63bffc884064"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Infrastructure Works" sheetId="5" r:id="R9e7f7318592b491b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Integrated Logistics Networks" sheetId="6" r:id="R90447147b5464cc1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dry Ports" sheetId="7" r:id="Racfac39a10e646e7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Economic Zones" sheetId="8" r:id="Rafe2f1ba14a64ad3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Shipyards" sheetId="9" r:id="Raf93330c10404b7f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Facilities" sheetId="10" r:id="R86b068ab6eb7412e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Corridors" sheetId="11" r:id="R7d16e700e6384651"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Regional Systems" sheetId="12" r:id="R641b5ba288c146b5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="System Nodes" sheetId="13" r:id="R43da3191139543c6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="System Links" sheetId="14" r:id="R3c4e5f2d7e0f477c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="System Dependencies" sheetId="15" r:id="Ra41d2ede1b88431e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Streamlit Map" sheetId="16" r:id="R9d7ad3e0c70247f1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tradeability Assessments" sheetId="17" r:id="R4a0117ef5f844d39"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="R213a76c3faf04771"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assets" sheetId="2" r:id="R35804a35340148e0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Asset Constraints" sheetId="3" r:id="R7d91a0e4ae684a62"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Infrastructure Connections" sheetId="4" r:id="R3cee6c139d4a4597"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Infrastructure Works" sheetId="5" r:id="R97c61d5eef9a4811"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Integrated Logistics Networks" sheetId="6" r:id="Ra2ba097ff4c94cd4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dry Ports" sheetId="7" r:id="R7677a1b5b26044cc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Economic Zones" sheetId="8" r:id="R60eb5e82c4ef4557"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Shipyards" sheetId="9" r:id="R16e1c9722bc54201"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Facilities" sheetId="10" r:id="R7a99e9ede99b4199"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Corridors" sheetId="11" r:id="R6da01b08e3884286"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Regional Systems" sheetId="12" r:id="Re5860ddb5dc046d2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="System Nodes" sheetId="13" r:id="R034f6fb739764dfe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="System Links" sheetId="14" r:id="Rda1c9179bf824aa3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="System Dependencies" sheetId="15" r:id="R7c2d5b23e13d477e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Streamlit Map" sheetId="16" r:id="Rb4e73051e5ce4f1b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tradeability Assessments" sheetId="17" r:id="R59fce974af7f4b2f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -78,7 +78,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="16">
+  <x:cellXfs count="17">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -103,6 +103,7 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -926,6 +927,82 @@
       </x:c>
       <x:c r="N9" s="14"/>
     </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="14" t="str">
+        <x:v>FAC_INOCEA_001</x:v>
+      </x:c>
+      <x:c r="B10" s="14" t="str">
+        <x:v>ASSET_INOCEA_001</x:v>
+      </x:c>
+      <x:c r="C10" s="14" t="str">
+        <x:v>COMP_DAVIE</x:v>
+      </x:c>
+      <x:c r="D10" s="14" t="str">
+        <x:v>Davie National Icebreaker Centre</x:v>
+      </x:c>
+      <x:c r="E10" s="14" t="str">
+        <x:v>Icebreaker production / program facility</x:v>
+      </x:c>
+      <x:c r="F10" s="14" t="str">
+        <x:v>Lévis, Québec</x:v>
+      </x:c>
+      <x:c r="G10" s="14" t="str">
+        <x:v>Canada</x:v>
+      </x:c>
+      <x:c r="H10" s="14" t="str"/>
+      <x:c r="I10" s="14" t="str"/>
+      <x:c r="J10" s="14" t="str"/>
+      <x:c r="K10" s="14" t="str">
+        <x:v>Operating / expanding</x:v>
+      </x:c>
+      <x:c r="L10" s="14" t="str">
+        <x:v>SRC_V1251_001</x:v>
+      </x:c>
+      <x:c r="M10" s="14" t="str">
+        <x:v>https://www.inocea.com/</x:v>
+      </x:c>
+      <x:c r="N10" s="14" t="str">
+        <x:v>Building and maintaining Canada's polar icebreaker fleet</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="14" t="str">
+        <x:v>FAC_INOCEA_002</x:v>
+      </x:c>
+      <x:c r="B11" s="14" t="str">
+        <x:v>ASSET_INOCEA_001</x:v>
+      </x:c>
+      <x:c r="C11" s="14" t="str">
+        <x:v>COMP_DAVIE</x:v>
+      </x:c>
+      <x:c r="D11" s="14" t="str">
+        <x:v>Davie Naval Maintenance Centre</x:v>
+      </x:c>
+      <x:c r="E11" s="14" t="str">
+        <x:v>Naval maintenance facility</x:v>
+      </x:c>
+      <x:c r="F11" s="14" t="str">
+        <x:v>Lévis, Québec</x:v>
+      </x:c>
+      <x:c r="G11" s="14" t="str">
+        <x:v>Canada</x:v>
+      </x:c>
+      <x:c r="H11" s="14" t="str"/>
+      <x:c r="I11" s="14" t="str"/>
+      <x:c r="J11" s="14" t="str"/>
+      <x:c r="K11" s="14" t="str">
+        <x:v>Operating</x:v>
+      </x:c>
+      <x:c r="L11" s="14" t="str">
+        <x:v>SRC_V1251_001</x:v>
+      </x:c>
+      <x:c r="M11" s="14" t="str">
+        <x:v>https://www.inocea.com/</x:v>
+      </x:c>
+      <x:c r="N11" s="14" t="str">
+        <x:v>Maintaining and upgrading Canada's warship fleet</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -6513,6 +6590,181 @@
       </x:c>
       <x:c r="K113" s="14" t="str">
         <x:v>SRC_V125_005</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="114">
+      <x:c r="A114" s="14" t="str">
+        <x:v>ASSET_INOCEA_001</x:v>
+      </x:c>
+      <x:c r="B114" s="14" t="str">
+        <x:v>COMP_DAVIE</x:v>
+      </x:c>
+      <x:c r="C114" s="14" t="str">
+        <x:v>Davie Lévis Shipyard</x:v>
+      </x:c>
+      <x:c r="D114" s="14" t="str">
+        <x:v>Shipyard / industrial complex</x:v>
+      </x:c>
+      <x:c r="E114" s="14" t="str">
+        <x:v>Lévis, Québec</x:v>
+      </x:c>
+      <x:c r="F114" s="14" t="str">
+        <x:v>Canada</x:v>
+      </x:c>
+      <x:c r="G114" s="14" t="str">
+        <x:v>Icebreaker, ferry and naval construction / repair</x:v>
+      </x:c>
+      <x:c r="H114" s="14" t="str">
+        <x:v>Maritime</x:v>
+      </x:c>
+      <x:c r="I114" s="14" t="str">
+        <x:v>Operating</x:v>
+      </x:c>
+      <x:c r="J114" s="14" t="str">
+        <x:v>Inocea / Davie</x:v>
+      </x:c>
+      <x:c r="K114" s="14" t="str">
+        <x:v>SRC_V1251_002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="115">
+      <x:c r="A115" s="14" t="str">
+        <x:v>ASSET_INOCEA_002</x:v>
+      </x:c>
+      <x:c r="B115" s="14" t="str">
+        <x:v>COMP_HELSINKI_SHIPYARD</x:v>
+      </x:c>
+      <x:c r="C115" s="14" t="str">
+        <x:v>Helsinki Shipyard</x:v>
+      </x:c>
+      <x:c r="D115" s="14" t="str">
+        <x:v>Shipyard / industrial complex</x:v>
+      </x:c>
+      <x:c r="E115" s="14" t="str">
+        <x:v>Helsinki</x:v>
+      </x:c>
+      <x:c r="F115" s="14" t="str">
+        <x:v>Finland</x:v>
+      </x:c>
+      <x:c r="G115" s="14" t="str">
+        <x:v>Arctic and icebreaker design / construction</x:v>
+      </x:c>
+      <x:c r="H115" s="14" t="str">
+        <x:v>Maritime</x:v>
+      </x:c>
+      <x:c r="I115" s="14" t="str">
+        <x:v>Operating</x:v>
+      </x:c>
+      <x:c r="J115" s="14" t="str">
+        <x:v>Davie / Inocea</x:v>
+      </x:c>
+      <x:c r="K115" s="14" t="str">
+        <x:v>SRC_V1251_003</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="116">
+      <x:c r="A116" s="14" t="str">
+        <x:v>ASSET_INOCEA_003</x:v>
+      </x:c>
+      <x:c r="B116" s="14" t="str">
+        <x:v>COMP_GULF_COPPER</x:v>
+      </x:c>
+      <x:c r="C116" s="14" t="str">
+        <x:v>Gulf Copper Galveston Shipyard</x:v>
+      </x:c>
+      <x:c r="D116" s="14" t="str">
+        <x:v>Shipyard / repair complex</x:v>
+      </x:c>
+      <x:c r="E116" s="14" t="str">
+        <x:v>Galveston, Texas</x:v>
+      </x:c>
+      <x:c r="F116" s="14" t="str">
+        <x:v>United States</x:v>
+      </x:c>
+      <x:c r="G116" s="14" t="str">
+        <x:v>Shipbuilding, repair, fabrication; U.S. Arctic shipbuilding capacity</x:v>
+      </x:c>
+      <x:c r="H116" s="14" t="str">
+        <x:v>Maritime</x:v>
+      </x:c>
+      <x:c r="I116" s="14" t="str">
+        <x:v>Operating</x:v>
+      </x:c>
+      <x:c r="J116" s="14" t="str">
+        <x:v>Inocea / Davie Defense</x:v>
+      </x:c>
+      <x:c r="K116" s="14" t="str">
+        <x:v>SRC_V1251_004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="117">
+      <x:c r="A117" s="14" t="str">
+        <x:v>ASSET_INOCEA_004</x:v>
+      </x:c>
+      <x:c r="B117" s="14" t="str">
+        <x:v>COMP_GULF_COPPER</x:v>
+      </x:c>
+      <x:c r="C117" s="14" t="str">
+        <x:v>Gulf Copper Port Arthur Facility</x:v>
+      </x:c>
+      <x:c r="D117" s="14" t="str">
+        <x:v>Shipyard / fabrication complex</x:v>
+      </x:c>
+      <x:c r="E117" s="14" t="str">
+        <x:v>Port Arthur, Texas</x:v>
+      </x:c>
+      <x:c r="F117" s="14" t="str">
+        <x:v>United States</x:v>
+      </x:c>
+      <x:c r="G117" s="14" t="str">
+        <x:v>Shipbuilding and fabrication</x:v>
+      </x:c>
+      <x:c r="H117" s="14" t="str">
+        <x:v>Maritime</x:v>
+      </x:c>
+      <x:c r="I117" s="14" t="str">
+        <x:v>Operating</x:v>
+      </x:c>
+      <x:c r="J117" s="14" t="str">
+        <x:v>Inocea / Davie Defense</x:v>
+      </x:c>
+      <x:c r="K117" s="14" t="str">
+        <x:v>SRC_V1251_004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="118">
+      <x:c r="A118" s="14" t="str">
+        <x:v>ASSET_INOCEA_005</x:v>
+      </x:c>
+      <x:c r="B118" s="14" t="str">
+        <x:v>COMP_SATA_SHIPBUILDING</x:v>
+      </x:c>
+      <x:c r="C118" s="14" t="str">
+        <x:v>Sata Shipbuilding Pori</x:v>
+      </x:c>
+      <x:c r="D118" s="14" t="str">
+        <x:v>Heavy fabrication / shipbuilding facility</x:v>
+      </x:c>
+      <x:c r="E118" s="14" t="str">
+        <x:v>Pori</x:v>
+      </x:c>
+      <x:c r="F118" s="14" t="str">
+        <x:v>Finland</x:v>
+      </x:c>
+      <x:c r="G118" s="14" t="str">
+        <x:v>Heavy industrial fabrication for marine, offshore and government vessels</x:v>
+      </x:c>
+      <x:c r="H118" s="14" t="str">
+        <x:v>Maritime / Industrial</x:v>
+      </x:c>
+      <x:c r="I118" s="14" t="str">
+        <x:v>Operating</x:v>
+      </x:c>
+      <x:c r="J118" s="14" t="str">
+        <x:v>Inocea</x:v>
+      </x:c>
+      <x:c r="K118" s="14" t="str">
+        <x:v>SRC_V1251_001</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -11108,6 +11360,151 @@
         <x:v>SRC_0355</x:v>
       </x:c>
     </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="14" t="str">
+        <x:v>YARD_INOCEA_001</x:v>
+      </x:c>
+      <x:c r="B31" s="14" t="str">
+        <x:v>Davie Shipbuilding</x:v>
+      </x:c>
+      <x:c r="C31" s="14" t="str">
+        <x:v>Canada</x:v>
+      </x:c>
+      <x:c r="D31" s="14" t="str">
+        <x:v>Lévis, Québec</x:v>
+      </x:c>
+      <x:c r="E31" s="14" t="str">
+        <x:v>Government / commercial shipbuilding</x:v>
+      </x:c>
+      <x:c r="F31" s="14" t="str">
+        <x:v>Icebreakers; ferries; warships</x:v>
+      </x:c>
+      <x:c r="G31" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="H31" s="14" t="str">
+        <x:v>Inocea group shipyard; six Program Icebreakers awarded in 2026</x:v>
+      </x:c>
+      <x:c r="I31" s="14" t="str">
+        <x:v>SRC_V1251_002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="14" t="str">
+        <x:v>YARD_INOCEA_002</x:v>
+      </x:c>
+      <x:c r="B32" s="14" t="str">
+        <x:v>Helsinki Shipyard</x:v>
+      </x:c>
+      <x:c r="C32" s="14" t="str">
+        <x:v>Finland</x:v>
+      </x:c>
+      <x:c r="D32" s="14" t="str">
+        <x:v>Helsinki</x:v>
+      </x:c>
+      <x:c r="E32" s="14" t="str">
+        <x:v>Government / commercial shipbuilding</x:v>
+      </x:c>
+      <x:c r="F32" s="14" t="str">
+        <x:v>Icebreakers; Arctic vessels; cruise; ferries</x:v>
+      </x:c>
+      <x:c r="G32" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="H32" s="14" t="str">
+        <x:v>Davie acquisition completed 3 Nov 2023</x:v>
+      </x:c>
+      <x:c r="I32" s="14" t="str">
+        <x:v>SRC_V1251_003</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="14" t="str">
+        <x:v>YARD_INOCEA_003</x:v>
+      </x:c>
+      <x:c r="B33" s="14" t="str">
+        <x:v>Gulf Copper - Galveston</x:v>
+      </x:c>
+      <x:c r="C33" s="14" t="str">
+        <x:v>United States</x:v>
+      </x:c>
+      <x:c r="D33" s="14" t="str">
+        <x:v>Galveston, Texas</x:v>
+      </x:c>
+      <x:c r="E33" s="14" t="str">
+        <x:v>Government / commercial shipbuilding</x:v>
+      </x:c>
+      <x:c r="F33" s="14" t="str">
+        <x:v>Arctic Security Cutters; repair; fabrication</x:v>
+      </x:c>
+      <x:c r="G33" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="H33" s="14" t="str">
+        <x:v>Acquired by Davie Defense in 2025</x:v>
+      </x:c>
+      <x:c r="I33" s="14" t="str">
+        <x:v>SRC_V1251_004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="14" t="str">
+        <x:v>YARD_INOCEA_004</x:v>
+      </x:c>
+      <x:c r="B34" s="14" t="str">
+        <x:v>Gulf Copper - Port Arthur</x:v>
+      </x:c>
+      <x:c r="C34" s="14" t="str">
+        <x:v>United States</x:v>
+      </x:c>
+      <x:c r="D34" s="14" t="str">
+        <x:v>Port Arthur, Texas</x:v>
+      </x:c>
+      <x:c r="E34" s="14" t="str">
+        <x:v>Government / industrial fabrication</x:v>
+      </x:c>
+      <x:c r="F34" s="14" t="str">
+        <x:v>Shipbuilding; fabrication; repair</x:v>
+      </x:c>
+      <x:c r="G34" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="H34" s="14" t="str">
+        <x:v>Acquired by Davie Defense in 2025</x:v>
+      </x:c>
+      <x:c r="I34" s="14" t="str">
+        <x:v>SRC_V1251_004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="14" t="str">
+        <x:v>YARD_INOCEA_005</x:v>
+      </x:c>
+      <x:c r="B35" s="14" t="str">
+        <x:v>Sata Shipbuilding</x:v>
+      </x:c>
+      <x:c r="C35" s="14" t="str">
+        <x:v>Finland</x:v>
+      </x:c>
+      <x:c r="D35" s="14" t="str">
+        <x:v>Pori</x:v>
+      </x:c>
+      <x:c r="E35" s="14" t="str">
+        <x:v>Heavy industrial fabrication</x:v>
+      </x:c>
+      <x:c r="F35" s="14" t="str">
+        <x:v>Icebreakers; offshore; special-purpose vessels</x:v>
+      </x:c>
+      <x:c r="G35" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="H35" s="14" t="str">
+        <x:v>Inocea Finland fabrication platform</x:v>
+      </x:c>
+      <x:c r="I35" s="14" t="str">
+        <x:v>SRC_V1251_001</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/data/06_infrastructure.xlsx
+++ b/data/06_infrastructure.xlsx
@@ -2,23 +2,23 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="R213a76c3faf04771"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assets" sheetId="2" r:id="R35804a35340148e0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Asset Constraints" sheetId="3" r:id="R7d91a0e4ae684a62"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Infrastructure Connections" sheetId="4" r:id="R3cee6c139d4a4597"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Infrastructure Works" sheetId="5" r:id="R97c61d5eef9a4811"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Integrated Logistics Networks" sheetId="6" r:id="Ra2ba097ff4c94cd4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dry Ports" sheetId="7" r:id="R7677a1b5b26044cc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Economic Zones" sheetId="8" r:id="R60eb5e82c4ef4557"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Shipyards" sheetId="9" r:id="R16e1c9722bc54201"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Facilities" sheetId="10" r:id="R7a99e9ede99b4199"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Corridors" sheetId="11" r:id="R6da01b08e3884286"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Regional Systems" sheetId="12" r:id="Re5860ddb5dc046d2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="System Nodes" sheetId="13" r:id="R034f6fb739764dfe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="System Links" sheetId="14" r:id="Rda1c9179bf824aa3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="System Dependencies" sheetId="15" r:id="R7c2d5b23e13d477e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Streamlit Map" sheetId="16" r:id="Rb4e73051e5ce4f1b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tradeability Assessments" sheetId="17" r:id="R59fce974af7f4b2f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="Rd21befb55c474df2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assets" sheetId="2" r:id="R4fbfe266707c4e56"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Asset Constraints" sheetId="3" r:id="R4419fb25eaa2449b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Infrastructure Connections" sheetId="4" r:id="R63ea8e28d9bf4df7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Infrastructure Works" sheetId="5" r:id="R37a2d131fec04ff8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Integrated Logistics Networks" sheetId="6" r:id="R8509fda9e9a148a2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dry Ports" sheetId="7" r:id="R109d41ba8b4c40db"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Economic Zones" sheetId="8" r:id="R216bb1b4ca18499f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Shipyards" sheetId="9" r:id="R4f55c3c1e6844c9e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Facilities" sheetId="10" r:id="R208c23ff260f480b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Corridors" sheetId="11" r:id="R91199285fc8a43e4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Regional Systems" sheetId="12" r:id="R960024b908654a2a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="System Nodes" sheetId="13" r:id="Re14d02432cd04504"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="System Links" sheetId="14" r:id="R8dfa606780a74c8e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="System Dependencies" sheetId="15" r:id="R87efa78f82bd4595"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Streamlit Map" sheetId="16" r:id="R1b95235898ae40fc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tradeability Assessments" sheetId="17" r:id="R2eb125ae77c64fcb"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1003,6 +1003,166 @@
         <x:v>Maintaining and upgrading Canada's warship fleet</x:v>
       </x:c>
     </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="14" t="str">
+        <x:v>FAC_GENOA_001</x:v>
+      </x:c>
+      <x:c r="B12" s="14" t="str">
+        <x:v>ASSET_GENOA_BREAKWATER</x:v>
+      </x:c>
+      <x:c r="C12" s="14" t="str">
+        <x:v>COMP_WLSPA</x:v>
+      </x:c>
+      <x:c r="D12" s="14" t="str">
+        <x:v>New Genoa Breakwater main structure</x:v>
+      </x:c>
+      <x:c r="E12" s="14" t="str">
+        <x:v>Breakwater</x:v>
+      </x:c>
+      <x:c r="F12" s="14" t="str">
+        <x:v>Offshore Genoa</x:v>
+      </x:c>
+      <x:c r="G12" s="14" t="str">
+        <x:v>Italy</x:v>
+      </x:c>
+      <x:c r="H12" s="14" t="str">
+        <x:v>6200</x:v>
+      </x:c>
+      <x:c r="I12" s="14" t="str"/>
+      <x:c r="J12" s="14" t="str"/>
+      <x:c r="K12" s="14" t="str">
+        <x:v>Under construction</x:v>
+      </x:c>
+      <x:c r="L12" s="14" t="str">
+        <x:v>SRC1261_002</x:v>
+      </x:c>
+      <x:c r="M12" s="14" t="str">
+        <x:v>https://www.portsofgenoa.com/it/nuova-diga-foranea-di-genova/il-progetto.html</x:v>
+      </x:c>
+      <x:c r="N12" s="14" t="str">
+        <x:v>Approx. 6.2 km overall planned length</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="14" t="str">
+        <x:v>FAC_GENOA_002</x:v>
+      </x:c>
+      <x:c r="B13" s="14" t="str">
+        <x:v>ASSET_GENOA_BREAKWATER</x:v>
+      </x:c>
+      <x:c r="C13" s="14" t="str">
+        <x:v>COMP_WLSPA</x:v>
+      </x:c>
+      <x:c r="D13" s="14" t="str">
+        <x:v>Eastern access channel</x:v>
+      </x:c>
+      <x:c r="E13" s="14" t="str">
+        <x:v>Navigation channel</x:v>
+      </x:c>
+      <x:c r="F13" s="14" t="str">
+        <x:v>Port of Genoa</x:v>
+      </x:c>
+      <x:c r="G13" s="14" t="str">
+        <x:v>Italy</x:v>
+      </x:c>
+      <x:c r="H13" s="14" t="str">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="I13" s="14" t="str"/>
+      <x:c r="J13" s="14" t="str"/>
+      <x:c r="K13" s="14" t="str">
+        <x:v>Under construction</x:v>
+      </x:c>
+      <x:c r="L13" s="14" t="str">
+        <x:v>SRC1261_002</x:v>
+      </x:c>
+      <x:c r="M13" s="14" t="str">
+        <x:v>https://www.portsofgenoa.com/it/nuova-diga-foranea-di-genova/il-progetto.html</x:v>
+      </x:c>
+      <x:c r="N13" s="14" t="str">
+        <x:v>Approx. 300 m wide</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="14" t="str">
+        <x:v>FAC_GENOA_003</x:v>
+      </x:c>
+      <x:c r="B14" s="14" t="str">
+        <x:v>ASSET_GENOA_BREAKWATER</x:v>
+      </x:c>
+      <x:c r="C14" s="14" t="str">
+        <x:v>COMP_WLSPA</x:v>
+      </x:c>
+      <x:c r="D14" s="14" t="str">
+        <x:v>Sampierdarena turning basin</x:v>
+      </x:c>
+      <x:c r="E14" s="14" t="str">
+        <x:v>Turning basin</x:v>
+      </x:c>
+      <x:c r="F14" s="14" t="str">
+        <x:v>Port of Genoa</x:v>
+      </x:c>
+      <x:c r="G14" s="14" t="str">
+        <x:v>Italy</x:v>
+      </x:c>
+      <x:c r="H14" s="14" t="str">
+        <x:v>800</x:v>
+      </x:c>
+      <x:c r="I14" s="14" t="str"/>
+      <x:c r="J14" s="14" t="str"/>
+      <x:c r="K14" s="14" t="str">
+        <x:v>Under construction</x:v>
+      </x:c>
+      <x:c r="L14" s="14" t="str">
+        <x:v>SRC1261_002</x:v>
+      </x:c>
+      <x:c r="M14" s="14" t="str">
+        <x:v>https://www.portsofgenoa.com/it/nuova-diga-foranea-di-genova/il-progetto.html</x:v>
+      </x:c>
+      <x:c r="N14" s="14" t="str">
+        <x:v>Approx. 800 m diameter</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="14" t="str">
+        <x:v>FAC_GENOA_004</x:v>
+      </x:c>
+      <x:c r="B15" s="14" t="str">
+        <x:v>ASSET_GENOA_BREAKWATER</x:v>
+      </x:c>
+      <x:c r="C15" s="14" t="str">
+        <x:v>COMP_WLSPA</x:v>
+      </x:c>
+      <x:c r="D15" s="14" t="str">
+        <x:v>Crest / wave wall</x:v>
+      </x:c>
+      <x:c r="E15" s="14" t="str">
+        <x:v>Breakwater superstructure</x:v>
+      </x:c>
+      <x:c r="F15" s="14" t="str">
+        <x:v>Port of Genoa</x:v>
+      </x:c>
+      <x:c r="G15" s="14" t="str">
+        <x:v>Italy</x:v>
+      </x:c>
+      <x:c r="H15" s="14" t="str">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="I15" s="14" t="str"/>
+      <x:c r="J15" s="14" t="str"/>
+      <x:c r="K15" s="14" t="str">
+        <x:v>Under construction</x:v>
+      </x:c>
+      <x:c r="L15" s="14" t="str">
+        <x:v>SRC1261_001</x:v>
+      </x:c>
+      <x:c r="M15" s="14" t="str">
+        <x:v>https://www.pergenovadigaforanea.it/en/news/work-begins-on-crest-wall-of-new-genoa-breakwater-new-caisson-also-installed-offshore.html</x:v>
+      </x:c>
+      <x:c r="N15" s="14" t="str">
+        <x:v>Approx. 7 m above sea level</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -6765,6 +6925,76 @@
       </x:c>
       <x:c r="K118" s="14" t="str">
         <x:v>SRC_V1251_001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="119">
+      <x:c r="A119" s="14" t="str">
+        <x:v>ASSET_GENOA_BREAKWATER</x:v>
+      </x:c>
+      <x:c r="B119" s="14" t="str">
+        <x:v>COMP_WLSPA</x:v>
+      </x:c>
+      <x:c r="C119" s="14" t="str">
+        <x:v>New Genoa Breakwater</x:v>
+      </x:c>
+      <x:c r="D119" s="14" t="str">
+        <x:v>Marine access infrastructure</x:v>
+      </x:c>
+      <x:c r="E119" s="14" t="str">
+        <x:v>Genoa</x:v>
+      </x:c>
+      <x:c r="F119" s="14" t="str">
+        <x:v>Italy</x:v>
+      </x:c>
+      <x:c r="G119" s="14" t="str">
+        <x:v>Breakwater / harbour access expansion for latest-generation ships</x:v>
+      </x:c>
+      <x:c r="H119" s="14" t="str">
+        <x:v>Maritime</x:v>
+      </x:c>
+      <x:c r="I119" s="14" t="str">
+        <x:v>Under construction</x:v>
+      </x:c>
+      <x:c r="J119" s="14" t="str">
+        <x:v>Commissioned by Western Ligurian Sea Port Authority</x:v>
+      </x:c>
+      <x:c r="K119" s="14" t="str">
+        <x:v>SRC1261_002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="120">
+      <x:c r="A120" s="14" t="str">
+        <x:v>ASSET_TERZO_VALICO</x:v>
+      </x:c>
+      <x:c r="B120" s="14" t="str">
+        <x:v>COMP_WEBUILD</x:v>
+      </x:c>
+      <x:c r="C120" s="14" t="str">
+        <x:v>Terzo Valico dei Giovi–Genoa Junction</x:v>
+      </x:c>
+      <x:c r="D120" s="14" t="str">
+        <x:v>Rail infrastructure project</x:v>
+      </x:c>
+      <x:c r="E120" s="14" t="str">
+        <x:v>Genoa / Liguria</x:v>
+      </x:c>
+      <x:c r="F120" s="14" t="str">
+        <x:v>Italy</x:v>
+      </x:c>
+      <x:c r="G120" s="14" t="str">
+        <x:v>Port-hinterland rail capacity and TEN-T Rhine-Alpine connection</x:v>
+      </x:c>
+      <x:c r="H120" s="14" t="str">
+        <x:v>Rail</x:v>
+      </x:c>
+      <x:c r="I120" s="14" t="str">
+        <x:v>Under construction</x:v>
+      </x:c>
+      <x:c r="J120" s="14" t="str">
+        <x:v>Strategic rail access project</x:v>
+      </x:c>
+      <x:c r="K120" s="14" t="str">
+        <x:v>SRC1261_003</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/data/06_infrastructure.xlsx
+++ b/data/06_infrastructure.xlsx
@@ -2,23 +2,23 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="Rd21befb55c474df2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assets" sheetId="2" r:id="R4fbfe266707c4e56"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Asset Constraints" sheetId="3" r:id="R4419fb25eaa2449b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Infrastructure Connections" sheetId="4" r:id="R63ea8e28d9bf4df7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Infrastructure Works" sheetId="5" r:id="R37a2d131fec04ff8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Integrated Logistics Networks" sheetId="6" r:id="R8509fda9e9a148a2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dry Ports" sheetId="7" r:id="R109d41ba8b4c40db"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Economic Zones" sheetId="8" r:id="R216bb1b4ca18499f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Shipyards" sheetId="9" r:id="R4f55c3c1e6844c9e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Facilities" sheetId="10" r:id="R208c23ff260f480b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Corridors" sheetId="11" r:id="R91199285fc8a43e4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Regional Systems" sheetId="12" r:id="R960024b908654a2a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="System Nodes" sheetId="13" r:id="Re14d02432cd04504"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="System Links" sheetId="14" r:id="R8dfa606780a74c8e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="System Dependencies" sheetId="15" r:id="R87efa78f82bd4595"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Streamlit Map" sheetId="16" r:id="R1b95235898ae40fc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tradeability Assessments" sheetId="17" r:id="R2eb125ae77c64fcb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="R72d2ce50d1ef4d68"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assets" sheetId="2" r:id="R236bb66a61fe4326"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Asset Constraints" sheetId="3" r:id="Ra1c2d6e5285f43d1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Infrastructure Connections" sheetId="4" r:id="R3a949ecab53e433d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Infrastructure Works" sheetId="5" r:id="R9460e11cfc284f11"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Integrated Logistics Networks" sheetId="6" r:id="R28bd10fe9a614a83"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dry Ports" sheetId="7" r:id="R376a588c9c1a413d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Economic Zones" sheetId="8" r:id="Rb88eaebcbc4c4189"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Shipyards" sheetId="9" r:id="R241bde74193c45e7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Facilities" sheetId="10" r:id="Ref2557ca883c4ffc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Corridors" sheetId="11" r:id="R64b6443c9a6e4e04"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Regional Systems" sheetId="12" r:id="R119cacd0d1da4627"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="System Nodes" sheetId="13" r:id="Rbd3c43ac4e67494f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="System Links" sheetId="14" r:id="Rae7e6ea65b714f0e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="System Dependencies" sheetId="15" r:id="Red5a440adf1548ca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Streamlit Map" sheetId="16" r:id="R865e12aa36a340af"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tradeability Assessments" sheetId="17" r:id="R95df0df5a3ac4bdd"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -6997,6 +6997,41 @@
         <x:v>SRC1261_003</x:v>
       </x:c>
     </x:row>
+    <x:row r="121">
+      <x:c r="A121" t="str">
+        <x:v>ASSET_ARCTIC_LNG2</x:v>
+      </x:c>
+      <x:c r="B121" t="str">
+        <x:v>COMP_ARCTIC_LNG2</x:v>
+      </x:c>
+      <x:c r="C121" t="str">
+        <x:v>Arctic LNG 2</x:v>
+      </x:c>
+      <x:c r="D121" t="str">
+        <x:v>LNG liquefaction project</x:v>
+      </x:c>
+      <x:c r="E121" t="str">
+        <x:v>Gydan Peninsula / Russian Arctic</x:v>
+      </x:c>
+      <x:c r="F121" t="str">
+        <x:v>Russia</x:v>
+      </x:c>
+      <x:c r="G121" t="str">
+        <x:v>Planned 19.8 million tonnes/year LNG export project</x:v>
+      </x:c>
+      <x:c r="H121" t="str">
+        <x:v>Maritime / energy</x:v>
+      </x:c>
+      <x:c r="I121" t="str">
+        <x:v>Operating / sanctions constrained</x:v>
+      </x:c>
+      <x:c r="J121" t="str">
+        <x:v>NOVATEK-led; reported 60% NOVATEK interest</x:v>
+      </x:c>
+      <x:c r="K121" t="str">
+        <x:v>SRC134_008</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/data/06_infrastructure.xlsx
+++ b/data/06_infrastructure.xlsx
@@ -2,23 +2,23 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="R72d2ce50d1ef4d68"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assets" sheetId="2" r:id="R236bb66a61fe4326"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Asset Constraints" sheetId="3" r:id="Ra1c2d6e5285f43d1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Infrastructure Connections" sheetId="4" r:id="R3a949ecab53e433d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Infrastructure Works" sheetId="5" r:id="R9460e11cfc284f11"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Integrated Logistics Networks" sheetId="6" r:id="R28bd10fe9a614a83"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dry Ports" sheetId="7" r:id="R376a588c9c1a413d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Economic Zones" sheetId="8" r:id="Rb88eaebcbc4c4189"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Shipyards" sheetId="9" r:id="R241bde74193c45e7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Facilities" sheetId="10" r:id="Ref2557ca883c4ffc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Corridors" sheetId="11" r:id="R64b6443c9a6e4e04"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Regional Systems" sheetId="12" r:id="R119cacd0d1da4627"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="System Nodes" sheetId="13" r:id="Rbd3c43ac4e67494f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="System Links" sheetId="14" r:id="Rae7e6ea65b714f0e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="System Dependencies" sheetId="15" r:id="Red5a440adf1548ca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Streamlit Map" sheetId="16" r:id="R865e12aa36a340af"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tradeability Assessments" sheetId="17" r:id="R95df0df5a3ac4bdd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="Rd21befb55c474df2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assets" sheetId="2" r:id="R4fbfe266707c4e56"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Asset Constraints" sheetId="3" r:id="R4419fb25eaa2449b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Infrastructure Connections" sheetId="4" r:id="R63ea8e28d9bf4df7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Infrastructure Works" sheetId="5" r:id="R37a2d131fec04ff8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Integrated Logistics Networks" sheetId="6" r:id="R8509fda9e9a148a2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dry Ports" sheetId="7" r:id="R109d41ba8b4c40db"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Economic Zones" sheetId="8" r:id="R216bb1b4ca18499f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Shipyards" sheetId="9" r:id="R4f55c3c1e6844c9e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Facilities" sheetId="10" r:id="R208c23ff260f480b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Corridors" sheetId="11" r:id="R91199285fc8a43e4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Regional Systems" sheetId="12" r:id="R960024b908654a2a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="System Nodes" sheetId="13" r:id="Re14d02432cd04504"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="System Links" sheetId="14" r:id="R8dfa606780a74c8e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="System Dependencies" sheetId="15" r:id="R87efa78f82bd4595"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Streamlit Map" sheetId="16" r:id="R1b95235898ae40fc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tradeability Assessments" sheetId="17" r:id="R2eb125ae77c64fcb"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -6997,41 +6997,6 @@
         <x:v>SRC1261_003</x:v>
       </x:c>
     </x:row>
-    <x:row r="121">
-      <x:c r="A121" t="str">
-        <x:v>ASSET_ARCTIC_LNG2</x:v>
-      </x:c>
-      <x:c r="B121" t="str">
-        <x:v>COMP_ARCTIC_LNG2</x:v>
-      </x:c>
-      <x:c r="C121" t="str">
-        <x:v>Arctic LNG 2</x:v>
-      </x:c>
-      <x:c r="D121" t="str">
-        <x:v>LNG liquefaction project</x:v>
-      </x:c>
-      <x:c r="E121" t="str">
-        <x:v>Gydan Peninsula / Russian Arctic</x:v>
-      </x:c>
-      <x:c r="F121" t="str">
-        <x:v>Russia</x:v>
-      </x:c>
-      <x:c r="G121" t="str">
-        <x:v>Planned 19.8 million tonnes/year LNG export project</x:v>
-      </x:c>
-      <x:c r="H121" t="str">
-        <x:v>Maritime / energy</x:v>
-      </x:c>
-      <x:c r="I121" t="str">
-        <x:v>Operating / sanctions constrained</x:v>
-      </x:c>
-      <x:c r="J121" t="str">
-        <x:v>NOVATEK-led; reported 60% NOVATEK interest</x:v>
-      </x:c>
-      <x:c r="K121" t="str">
-        <x:v>SRC134_008</x:v>
-      </x:c>
-    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/data/06_infrastructure.xlsx
+++ b/data/06_infrastructure.xlsx
@@ -2,23 +2,23 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="Rd21befb55c474df2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assets" sheetId="2" r:id="R4fbfe266707c4e56"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Asset Constraints" sheetId="3" r:id="R4419fb25eaa2449b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Infrastructure Connections" sheetId="4" r:id="R63ea8e28d9bf4df7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Infrastructure Works" sheetId="5" r:id="R37a2d131fec04ff8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Integrated Logistics Networks" sheetId="6" r:id="R8509fda9e9a148a2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dry Ports" sheetId="7" r:id="R109d41ba8b4c40db"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Economic Zones" sheetId="8" r:id="R216bb1b4ca18499f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Shipyards" sheetId="9" r:id="R4f55c3c1e6844c9e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Facilities" sheetId="10" r:id="R208c23ff260f480b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Corridors" sheetId="11" r:id="R91199285fc8a43e4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Regional Systems" sheetId="12" r:id="R960024b908654a2a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="System Nodes" sheetId="13" r:id="Re14d02432cd04504"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="System Links" sheetId="14" r:id="R8dfa606780a74c8e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="System Dependencies" sheetId="15" r:id="R87efa78f82bd4595"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Streamlit Map" sheetId="16" r:id="R1b95235898ae40fc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tradeability Assessments" sheetId="17" r:id="R2eb125ae77c64fcb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="R32a8e1ab96a14966"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assets" sheetId="2" r:id="Raa29a212d17b46f0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Asset Constraints" sheetId="3" r:id="R70ddb95bbbf94b24"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Infrastructure Connections" sheetId="4" r:id="R149055f33fae40be"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Infrastructure Works" sheetId="5" r:id="R575e98d70e194850"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Integrated Logistics Networks" sheetId="6" r:id="R14254c3896194552"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dry Ports" sheetId="7" r:id="R55376acae8d44863"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Economic Zones" sheetId="8" r:id="Rb2386b7c11d04fec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Shipyards" sheetId="9" r:id="R084d28f9a93642da"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Facilities" sheetId="10" r:id="R4329dc3914d3421d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Corridors" sheetId="11" r:id="Rb95af1a3cdd84a0d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Regional Systems" sheetId="12" r:id="Rc096a94ebce64f7f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="System Nodes" sheetId="13" r:id="R5087ec6295364069"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="System Links" sheetId="14" r:id="R6f4950711497486d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="System Dependencies" sheetId="15" r:id="R259deda3306349fe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Streamlit Map" sheetId="16" r:id="R9a3147794a274b68"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tradeability Assessments" sheetId="17" r:id="R51e8b78347884714"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -11735,6 +11735,35 @@
         <x:v>SRC_V1251_001</x:v>
       </x:c>
     </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="14" t="str">
+        <x:v>YARD_QINGDAO_BEIHAI</x:v>
+      </x:c>
+      <x:c r="B36" s="14" t="str">
+        <x:v>Qingdao Beihai Shipbuilding</x:v>
+      </x:c>
+      <x:c r="C36" s="14" t="str">
+        <x:v>China</x:v>
+      </x:c>
+      <x:c r="D36" s="14" t="str">
+        <x:v>Qingdao, Shandong</x:v>
+      </x:c>
+      <x:c r="E36" s="14" t="str">
+        <x:v>Commercial shipbuilding and repair</x:v>
+      </x:c>
+      <x:c r="F36" s="14" t="str">
+        <x:v>Bulk carriers; commercial vessels; repair</x:v>
+      </x:c>
+      <x:c r="G36" s="14" t="str">
+        <x:v>Active / incident recovery</x:v>
+      </x:c>
+      <x:c r="H36" s="14" t="str">
+        <x:v>CSSC-controlled yard; reported capacity around 3m dwt annual shipbuilding and about 212 vessel repairs/year. Ocean Melody fire on 10 Sep 2026 killed 25.</x:v>
+      </x:c>
+      <x:c r="I36" s="14" t="str">
+        <x:v>SRC260911_001</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/data/06_infrastructure.xlsx
+++ b/data/06_infrastructure.xlsx
@@ -2,23 +2,23 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="R32a8e1ab96a14966"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assets" sheetId="2" r:id="Raa29a212d17b46f0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Asset Constraints" sheetId="3" r:id="R70ddb95bbbf94b24"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Infrastructure Connections" sheetId="4" r:id="R149055f33fae40be"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Infrastructure Works" sheetId="5" r:id="R575e98d70e194850"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Integrated Logistics Networks" sheetId="6" r:id="R14254c3896194552"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dry Ports" sheetId="7" r:id="R55376acae8d44863"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Economic Zones" sheetId="8" r:id="Rb2386b7c11d04fec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Shipyards" sheetId="9" r:id="R084d28f9a93642da"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Facilities" sheetId="10" r:id="R4329dc3914d3421d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Corridors" sheetId="11" r:id="Rb95af1a3cdd84a0d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Regional Systems" sheetId="12" r:id="Rc096a94ebce64f7f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="System Nodes" sheetId="13" r:id="R5087ec6295364069"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="System Links" sheetId="14" r:id="R6f4950711497486d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="System Dependencies" sheetId="15" r:id="R259deda3306349fe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Streamlit Map" sheetId="16" r:id="R9a3147794a274b68"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tradeability Assessments" sheetId="17" r:id="R51e8b78347884714"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="Rf864f72ba64840f4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assets" sheetId="2" r:id="R38f70b2ac8c24cf9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Asset Constraints" sheetId="3" r:id="R19a2120947584bbc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Infrastructure Connections" sheetId="4" r:id="R4f52685d723449b4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Infrastructure Works" sheetId="5" r:id="R4d927c7597004fc4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Integrated Logistics Networks" sheetId="6" r:id="Rf38eccc49b7b4a32"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dry Ports" sheetId="7" r:id="R558fa786c4e34c28"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Economic Zones" sheetId="8" r:id="R57c3e7dfe5c04018"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Shipyards" sheetId="9" r:id="R907fac2169c64361"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Facilities" sheetId="10" r:id="R08abcc404cde4dc1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Corridors" sheetId="11" r:id="R437ef781f4a2486e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Regional Systems" sheetId="12" r:id="Rc6398c96c9fe4b48"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="System Nodes" sheetId="13" r:id="Rb9e7bb2aec164e1d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="System Links" sheetId="14" r:id="R8105e1fcc9d14695"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="System Dependencies" sheetId="15" r:id="R752c1741538843bc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Streamlit Map" sheetId="16" r:id="Refb9226175cc44ff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tradeability Assessments" sheetId="17" r:id="Re53b2f7fd1d64a06"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -6997,6 +6997,146 @@
         <x:v>SRC1261_003</x:v>
       </x:c>
     </x:row>
+    <x:row r="121">
+      <x:c r="A121" t="str">
+        <x:v>ASSET_BF_001</x:v>
+      </x:c>
+      <x:c r="B121" t="str">
+        <x:v>COMP_WMCT</x:v>
+      </x:c>
+      <x:c r="C121" t="str">
+        <x:v>Nador West Med Eastern Container Terminal</x:v>
+      </x:c>
+      <x:c r="D121" t="str">
+        <x:v>Container terminal</x:v>
+      </x:c>
+      <x:c r="E121" t="str">
+        <x:v>Nador West Med</x:v>
+      </x:c>
+      <x:c r="F121" t="str">
+        <x:v>Morocco</x:v>
+      </x:c>
+      <x:c r="G121" t="str">
+        <x:v>Eastern container terminal / transshipment gateway</x:v>
+      </x:c>
+      <x:c r="H121" t="str">
+        <x:v>Container</x:v>
+      </x:c>
+      <x:c r="I121" t="str">
+        <x:v>Operational readiness / pre-commercial</x:v>
+      </x:c>
+      <x:c r="J121" t="str">
+        <x:v>WMCT; Marsa Maroc 50%+1 / TIL 50%-1</x:v>
+      </x:c>
+      <x:c r="K121" t="str">
+        <x:v>SRC_BF_NADOR_MARSA26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="122">
+      <x:c r="A122" t="str">
+        <x:v>ASSET_BF_002</x:v>
+      </x:c>
+      <x:c r="B122" t="str">
+        <x:v>COMP_CMA_TERMINALS</x:v>
+      </x:c>
+      <x:c r="C122" t="str">
+        <x:v>Port of Beirut Container Terminal</x:v>
+      </x:c>
+      <x:c r="D122" t="str">
+        <x:v>Container terminal</x:v>
+      </x:c>
+      <x:c r="E122" t="str">
+        <x:v>Beirut</x:v>
+      </x:c>
+      <x:c r="F122" t="str">
+        <x:v>Lebanon</x:v>
+      </x:c>
+      <x:c r="G122" t="str">
+        <x:v>Lebanon gateway and Eastern Mediterranean transshipment terminal</x:v>
+      </x:c>
+      <x:c r="H122" t="str">
+        <x:v>Container</x:v>
+      </x:c>
+      <x:c r="I122" t="str">
+        <x:v>Operating / expanding</x:v>
+      </x:c>
+      <x:c r="J122" t="str">
+        <x:v>10-year CMA Terminals operating concession from March 2022</x:v>
+      </x:c>
+      <x:c r="K122" t="str">
+        <x:v>SRC_BF_BEIRUT_CMA22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="123">
+      <x:c r="A123" t="str">
+        <x:v>ASSET_BF_003</x:v>
+      </x:c>
+      <x:c r="B123" t="str">
+        <x:v>COMP_NELTUME</x:v>
+      </x:c>
+      <x:c r="C123" t="str">
+        <x:v>Montevideo Container Terminal (MCT)</x:v>
+      </x:c>
+      <x:c r="D123" t="str">
+        <x:v>Proposed container terminal</x:v>
+      </x:c>
+      <x:c r="E123" t="str">
+        <x:v>Port of Montevideo</x:v>
+      </x:c>
+      <x:c r="F123" t="str">
+        <x:v>Uruguay</x:v>
+      </x:c>
+      <x:c r="G123" t="str">
+        <x:v>Greenfield specialised container terminal / regional hub</x:v>
+      </x:c>
+      <x:c r="H123" t="str">
+        <x:v>Container</x:v>
+      </x:c>
+      <x:c r="I123" t="str">
+        <x:v>Proposed / government evaluation</x:v>
+      </x:c>
+      <x:c r="J123" t="str">
+        <x:v>Neltume privately initiated proposal</x:v>
+      </x:c>
+      <x:c r="K123" t="str">
+        <x:v>SRC_BF_NELTUME_SPLASH</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="124">
+      <x:c r="A124" t="str">
+        <x:v>ASSET_BF_004</x:v>
+      </x:c>
+      <x:c r="B124" t="str">
+        <x:v>COMP_TCP</x:v>
+      </x:c>
+      <x:c r="C124" t="str">
+        <x:v>Terminal Cuenca del Plata</x:v>
+      </x:c>
+      <x:c r="D124" t="str">
+        <x:v>Container terminal</x:v>
+      </x:c>
+      <x:c r="E124" t="str">
+        <x:v>Port of Montevideo</x:v>
+      </x:c>
+      <x:c r="F124" t="str">
+        <x:v>Uruguay</x:v>
+      </x:c>
+      <x:c r="G124" t="str">
+        <x:v>Existing specialised container terminal / competitor to proposed MCT</x:v>
+      </x:c>
+      <x:c r="H124" t="str">
+        <x:v>Container</x:v>
+      </x:c>
+      <x:c r="I124" t="str">
+        <x:v>Operating / expanding</x:v>
+      </x:c>
+      <x:c r="J124" t="str">
+        <x:v>80% private / 20% ANP structure</x:v>
+      </x:c>
+      <x:c r="K124" t="str">
+        <x:v>SRC_BF_TCP_ANP</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -9177,6 +9317,207 @@
       </x:c>
       <x:c r="M14" s="14" t="str">
         <x:v>SRC_0344</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" t="str">
+        <x:v>WORK_BF_001</x:v>
+      </x:c>
+      <x:c r="B15" t="str">
+        <x:v>COMP_WMCT</x:v>
+      </x:c>
+      <x:c r="C15" t="str">
+        <x:v>Nador West Med Eastern Container Terminal</x:v>
+      </x:c>
+      <x:c r="D15" t="str">
+        <x:v>Morocco</x:v>
+      </x:c>
+      <x:c r="E15" t="str">
+        <x:v>Commissioning / terminal development</x:v>
+      </x:c>
+      <x:c r="F15" t="str">
+        <x:v>Live operational trials completed using MSC NITA</x:v>
+      </x:c>
+      <x:c r="G15" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+      <x:c r="H15" t="str">
+        <x:v>Operational readiness / pre-commercial</x:v>
+      </x:c>
+      <x:c r="I15"/>
+      <x:c r="J15"/>
+      <x:c r="K15" t="str">
+        <x:v>1,520m quay; 18m draft; 70ha; 3.4m TEU ultimate capacity</x:v>
+      </x:c>
+      <x:c r="L15" t="str">
+        <x:v>Adds major MSC/TIL-linked transshipment capacity at Nador West Med</x:v>
+      </x:c>
+      <x:c r="M15" t="str">
+        <x:v>SRC_BF_NADOR_SPLASH</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" t="str">
+        <x:v>WORK_BF_002</x:v>
+      </x:c>
+      <x:c r="B16" t="str">
+        <x:v>COMP_CMA_TERMINALS</x:v>
+      </x:c>
+      <x:c r="C16" t="str">
+        <x:v>Port of Beirut Container Terminal</x:v>
+      </x:c>
+      <x:c r="D16" t="str">
+        <x:v>Lebanon</x:v>
+      </x:c>
+      <x:c r="E16" t="str">
+        <x:v>Terminal expansion</x:v>
+      </x:c>
+      <x:c r="F16" t="str">
+        <x:v>$100m capacity expansion centred on berth 16</x:v>
+      </x:c>
+      <x:c r="G16" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+      <x:c r="H16" t="str">
+        <x:v>Launched</x:v>
+      </x:c>
+      <x:c r="I16" t="n">
+        <x:v>100000000</x:v>
+      </x:c>
+      <x:c r="J16" t="str">
+        <x:v>USD</x:v>
+      </x:c>
+      <x:c r="K16" t="str">
+        <x:v>Capacity targeted from ~1.3m to 3.0m TEU by 2028; ~1.1km quay; &gt;16.5m draft</x:v>
+      </x:c>
+      <x:c r="L16" t="str">
+        <x:v>Rebuilds Beirut's regional transshipment/logistics role</x:v>
+      </x:c>
+      <x:c r="M16" t="str">
+        <x:v>SRC_BF_BEIRUT_SPLASH</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" t="str">
+        <x:v>WORK_BF_003</x:v>
+      </x:c>
+      <x:c r="B17" t="str">
+        <x:v>COMP_CMA_TERMINALS</x:v>
+      </x:c>
+      <x:c r="C17" t="str">
+        <x:v>Port of Beirut Container Terminal</x:v>
+      </x:c>
+      <x:c r="D17" t="str">
+        <x:v>Lebanon</x:v>
+      </x:c>
+      <x:c r="E17" t="str">
+        <x:v>Modernization / concession investment</x:v>
+      </x:c>
+      <x:c r="F17" t="str">
+        <x:v>2022 concession modernization plan</x:v>
+      </x:c>
+      <x:c r="G17" t="str">
+        <x:v>2022-02-17</x:v>
+      </x:c>
+      <x:c r="H17" t="str">
+        <x:v>Operating / implementation</x:v>
+      </x:c>
+      <x:c r="I17" t="n">
+        <x:v>33000000</x:v>
+      </x:c>
+      <x:c r="J17" t="str">
+        <x:v>USD</x:v>
+      </x:c>
+      <x:c r="K17" t="str">
+        <x:v>Infrastructure, equipment, technical facility, digital and environmental upgrades</x:v>
+      </x:c>
+      <x:c r="L17" t="str">
+        <x:v>Historical investment baseline before 2026 expansion</x:v>
+      </x:c>
+      <x:c r="M17" t="str">
+        <x:v>SRC_BF_BEIRUT_CMA22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" t="str">
+        <x:v>WORK_BF_004</x:v>
+      </x:c>
+      <x:c r="B18" t="str">
+        <x:v>COMP_NELTUME</x:v>
+      </x:c>
+      <x:c r="C18" t="str">
+        <x:v>Montevideo Container Terminal (MCT)</x:v>
+      </x:c>
+      <x:c r="D18" t="str">
+        <x:v>Uruguay</x:v>
+      </x:c>
+      <x:c r="E18" t="str">
+        <x:v>Greenfield terminal proposal</x:v>
+      </x:c>
+      <x:c r="F18" t="str">
+        <x:v>Neltume proposed new specialised container terminal</x:v>
+      </x:c>
+      <x:c r="G18" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="H18" t="str">
+        <x:v>Proposed / government evaluation</x:v>
+      </x:c>
+      <x:c r="I18" t="n">
+        <x:v>900000000</x:v>
+      </x:c>
+      <x:c r="J18" t="str">
+        <x:v>USD</x:v>
+      </x:c>
+      <x:c r="K18" t="str">
+        <x:v>1.15m TEU; 940m quay; ~38ha; two post-panamax positions plus barge berth; ~1,800 construction jobs</x:v>
+      </x:c>
+      <x:c r="L18" t="str">
+        <x:v>Would reshape container competition and Neltume exposure in Montevideo</x:v>
+      </x:c>
+      <x:c r="M18" t="str">
+        <x:v>SRC_BF_NELTUME_SPLASH</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" t="str">
+        <x:v>WORK_BF_005</x:v>
+      </x:c>
+      <x:c r="B19" t="str">
+        <x:v>COMP_TCP</x:v>
+      </x:c>
+      <x:c r="C19" t="str">
+        <x:v>Terminal Cuenca del Plata</x:v>
+      </x:c>
+      <x:c r="D19" t="str">
+        <x:v>Uruguay</x:v>
+      </x:c>
+      <x:c r="E19" t="str">
+        <x:v>Terminal expansion</x:v>
+      </x:c>
+      <x:c r="F19" t="str">
+        <x:v>Second container yard and new quay</x:v>
+      </x:c>
+      <x:c r="G19" t="str">
+        <x:v>2023-07-24</x:v>
+      </x:c>
+      <x:c r="H19" t="str">
+        <x:v>Authorized / development</x:v>
+      </x:c>
+      <x:c r="I19" t="n">
+        <x:v>600000000</x:v>
+      </x:c>
+      <x:c r="J19" t="str">
+        <x:v>USD</x:v>
+      </x:c>
+      <x:c r="K19" t="str">
+        <x:v>&gt;US$600m; 22ha second yard; 700m quay; 14m depth</x:v>
+      </x:c>
+      <x:c r="L19" t="str">
+        <x:v>Triples stated handling capability and anchors long-term TCP concession position</x:v>
+      </x:c>
+      <x:c r="M19" t="str">
+        <x:v>SRC_BF_TCP_ANP</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
